--- a/artfynd/A 43107-2023 artfynd.xlsx
+++ b/artfynd/A 43107-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43107-2023 artfynd.xlsx
+++ b/artfynd/A 43107-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56357315</v>
+        <v>56357313</v>
       </c>
       <c r="B2" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569156.7242578672</v>
+        <v>569122</v>
       </c>
       <c r="R2" t="n">
-        <v>7011497.200078044</v>
+        <v>7011345</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,21 +743,11 @@
           <t>2015-09-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-09-18</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -778,11 +763,11 @@
         </is>
       </c>
       <c r="AN2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>1 substratenheter # klen gammal tallåga</t>
+          <t>2 substratenheter # grova gamla tallågor på block</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -804,15 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>56357317</v>
+        <v>56357316</v>
       </c>
       <c r="B3" t="n">
-        <v>79433</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,21 +800,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1049</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -844,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569134.3214246393</v>
+        <v>569239</v>
       </c>
       <c r="R3" t="n">
-        <v>7011530.996579801</v>
+        <v>7011477</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -877,21 +857,11 @@
           <t>2015-09-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2015-09-18</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -907,11 +877,11 @@
         </is>
       </c>
       <c r="AN3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>1 substratenheter # grova gammal tallhögstubbe</t>
+          <t>3 substratenheter # grova gamla tallågor</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -933,15 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>56357314</v>
+        <v>103997292</v>
       </c>
       <c r="B4" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -949,37 +914,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Pikhöjden, nordost om, Jmt</t>
+          <t>Halbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569163.8793452184</v>
+        <v>569123</v>
       </c>
       <c r="R4" t="n">
-        <v>7011500.510627565</v>
+        <v>7011358</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1003,22 +968,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2015-09-18</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2015-09-18</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,47 +995,34 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>äldre tallskog på blockig morän</t>
-        </is>
-      </c>
-      <c r="AN4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>2 substratenheter # grov tallhögstubbe med spår av 4 bränder</t>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Via Johan Staaf</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>56357313</v>
+        <v>56357317</v>
       </c>
       <c r="B5" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,21 +1030,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>1049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1102,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569122.0513879382</v>
+        <v>569134</v>
       </c>
       <c r="R5" t="n">
-        <v>7011344.912510831</v>
+        <v>7011531</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1135,21 +1087,11 @@
           <t>2015-09-18</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2015-09-18</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1161,15 +1103,15 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>äldre tallskog på blockig morän</t>
+          <t>140-årig tallskog på blockig morän</t>
         </is>
       </c>
       <c r="AN5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>2 substratenheter # grova gamla tallågor på block</t>
+          <t>1 substratenheter # grova gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1191,15 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>56357316</v>
+        <v>97362352</v>
       </c>
       <c r="B6" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,37 +1144,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>1049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Pikhöjden, nordost om, Jmt</t>
+          <t>Nissemyran, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569239.3478535078</v>
+        <v>569144</v>
       </c>
       <c r="R6" t="n">
-        <v>7011477.324301938</v>
+        <v>7011434</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1261,22 +1198,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2015-09-18</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2015-09-18</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1288,47 +1215,34 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>140-årig tallskog på blockig morän</t>
-        </is>
-      </c>
-      <c r="AN6" t="n">
-        <v>3</v>
-      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>3 substratenheter # grova gamla tallågor</t>
+          <t>Kolad tallhögstubbe</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Via Johan Staaf</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>97362333</v>
+        <v>97362338</v>
       </c>
       <c r="B7" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,21 +1250,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1360,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569063.3882083312</v>
+        <v>569120</v>
       </c>
       <c r="R7" t="n">
-        <v>7011469.040883667</v>
+        <v>7011613</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1393,19 +1307,9 @@
           <t>2021-06-17</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-06-17</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1436,53 +1340,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>97362350</v>
+        <v>56357315</v>
       </c>
       <c r="B8" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>1503</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nissemyran, Jmt</t>
+          <t>Pikhöjden, nordost om, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569076.5471861656</v>
+        <v>569157</v>
       </c>
       <c r="R8" t="n">
-        <v>7011466.165607615</v>
+        <v>7011497</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1506,22 +1405,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-09-18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-09-18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1533,39 +1422,42 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>äldre tallskog på blockig morän</t>
+        </is>
+      </c>
+      <c r="AN8" t="n">
+        <v>1</v>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Äldre gran</t>
+          <t>1 substratenheter # klen gammal tallåga</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>97362347</v>
+        <v>103997241</v>
       </c>
       <c r="B9" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,34 +1465,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nissemyran, Jmt</t>
+          <t>Halbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>569169.689291648</v>
+        <v>569248</v>
       </c>
       <c r="R9" t="n">
-        <v>7011440.198870962</v>
+        <v>7011329</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1627,22 +1519,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1653,6 +1545,11 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1667,21 +1564,16 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>97362341</v>
+        <v>103997281</v>
       </c>
       <c r="B10" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,34 +1581,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nissemyran, Jmt</t>
+          <t>Halbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569064.2717524428</v>
+        <v>569069</v>
       </c>
       <c r="R10" t="n">
-        <v>7011469.961840461</v>
+        <v>7011448</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1743,22 +1635,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1770,9 +1662,9 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Sälg</t>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1788,56 +1680,51 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>97362344</v>
+        <v>103997267</v>
       </c>
       <c r="B11" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nissemyran, Jmt</t>
+          <t>Halbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569207.8089015677</v>
+        <v>568989</v>
       </c>
       <c r="R11" t="n">
-        <v>7011579.026541895</v>
+        <v>7011464</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1864,22 +1751,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1890,6 +1777,16 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1904,21 +1801,16 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>97362335</v>
+        <v>97362345</v>
       </c>
       <c r="B12" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1926,21 +1818,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1950,10 +1842,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569217.7824827663</v>
+        <v>569011</v>
       </c>
       <c r="R12" t="n">
-        <v>7011493.097917392</v>
+        <v>7011496</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1983,21 +1875,11 @@
           <t>2021-06-17</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-06-17</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2006,6 +1888,11 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Kolad tallstubbe</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2026,15 +1913,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>97362348</v>
+        <v>97362347</v>
       </c>
       <c r="B13" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2042,21 +1924,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2066,10 +1948,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569215.3545450632</v>
+        <v>569170</v>
       </c>
       <c r="R13" t="n">
-        <v>7011479.966346126</v>
+        <v>7011440</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2099,19 +1981,9 @@
           <t>2021-06-17</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2021-06-17</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2142,15 +2014,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>97362352</v>
+        <v>97362350</v>
       </c>
       <c r="B14" t="n">
-        <v>79433</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2158,21 +2025,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1049</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2182,10 +2049,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569143.6222787398</v>
+        <v>569076</v>
       </c>
       <c r="R14" t="n">
-        <v>7011434.227592845</v>
+        <v>7011466</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2215,21 +2082,11 @@
           <t>2021-06-17</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2021-06-17</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2241,7 +2098,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Kolad tallhögstubbe</t>
+          <t>Äldre gran</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2263,53 +2120,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>103997281</v>
+        <v>56357314</v>
       </c>
       <c r="B15" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4769</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Halbodarna, Jmt</t>
+          <t>Pikhöjden, nordost om, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569068.8077133502</v>
+        <v>569164</v>
       </c>
       <c r="R15" t="n">
-        <v>7011447.959077032</v>
+        <v>7011501</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2333,22 +2185,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>2015-09-18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>2015-09-18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2360,39 +2202,42 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>äldre tallskog på blockig morän</t>
+        </is>
+      </c>
+      <c r="AN15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>2 substratenheter # grov tallhögstubbe med spår av 4 bränder</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>103997292</v>
+        <v>97362348</v>
       </c>
       <c r="B16" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2400,34 +2245,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Halbodarna, Jmt</t>
+          <t>Nissemyran, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569122.6740497423</v>
+        <v>569215</v>
       </c>
       <c r="R16" t="n">
-        <v>7011358.005841793</v>
+        <v>7011480</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2454,22 +2299,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2021-06-17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2021-06-17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2480,11 +2315,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2499,21 +2329,16 @@
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>103997214</v>
+        <v>97362333</v>
       </c>
       <c r="B17" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2521,34 +2346,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Halbodarna, Jmt</t>
+          <t>Nissemyran, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569253.8960440678</v>
+        <v>569063</v>
       </c>
       <c r="R17" t="n">
-        <v>7011325.640311676</v>
+        <v>7011469</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2575,22 +2400,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>13:31</t>
+          <t>2021-06-17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:31</t>
+          <t>2021-06-17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2601,11 +2416,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2620,21 +2430,16 @@
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>103997241</v>
+        <v>97362341</v>
       </c>
       <c r="B18" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2642,34 +2447,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Halbodarna, Jmt</t>
+          <t>Nissemyran, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569247.9401062741</v>
+        <v>569064</v>
       </c>
       <c r="R18" t="n">
-        <v>7011329.571760437</v>
+        <v>7011470</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2696,22 +2501,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2021-06-17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2021-06-17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2723,9 +2518,9 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
-      <c r="AS18" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2741,21 +2536,16 @@
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>103997267</v>
+        <v>97362335</v>
       </c>
       <c r="B19" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2763,34 +2553,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Halbodarna, Jmt</t>
+          <t>Nissemyran, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>568989.4216837514</v>
+        <v>569218</v>
       </c>
       <c r="R19" t="n">
-        <v>7011464.300508332</v>
+        <v>7011493</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2817,22 +2607,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:49</t>
+          <t>2021-06-17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:49</t>
+          <t>2021-06-17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2843,16 +2623,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
-      </c>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2866,6 +2636,223 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>97362344</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Nissemyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>569208</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7011579</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2021-06-17</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2021-06-17</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>103997214</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Halbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>569254</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7011325</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>

--- a/artfynd/A 43107-2023 artfynd.xlsx
+++ b/artfynd/A 43107-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56357313</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56357316</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1016,6 +1031,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103997292</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1130,6 +1150,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56357317</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1236,6 +1261,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362352</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1337,6 +1367,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362338</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1451,6 +1486,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56357315</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1567,6 +1607,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103997241</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1683,6 +1728,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103997281</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1804,6 +1854,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103997267</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1910,6 +1965,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362345</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2011,6 +2071,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362347</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2117,6 +2182,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362350</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2231,6 +2301,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56357314</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2332,6 +2407,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362348</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2433,6 +2513,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362333</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2539,6 +2624,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362341</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2640,6 +2730,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362335</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2741,6 +2836,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362344</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2857,8 +2957,35 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103997214</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 43107-2023 artfynd.xlsx
+++ b/artfynd/A 43107-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ21"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1039,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>56357317</v>
+        <v>135641212</v>
       </c>
       <c r="B5" t="n">
-        <v>81312</v>
+        <v>79077</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1050,37 +1050,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1049</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Pikhöjden, nordost om, Jmt</t>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569134</v>
+        <v>569119</v>
       </c>
       <c r="R5" t="n">
-        <v>7011531</v>
+        <v>7011357</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2015-09-18</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2015-09-18</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,44 +1121,42 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>140-årig tallskog på blockig morän</t>
-        </is>
-      </c>
-      <c r="AN5" t="n">
-        <v>1</v>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>1 substratenheter # grova gammal tallhögstubbe</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/56357317</t>
+          <t>https://artportalen.se/Sighting/135641212</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97362352</v>
+        <v>56357317</v>
       </c>
       <c r="B6" t="n">
         <v>81312</v>
@@ -1189,17 +1187,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nissemyran, Jmt</t>
+          <t>Pikhöjden, nordost om, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569144</v>
+        <v>569134</v>
       </c>
       <c r="R6" t="n">
-        <v>7011434</v>
+        <v>7011531</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1223,12 +1221,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2015-09-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2015-09-18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,39 +1238,47 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>140-årig tallskog på blockig morän</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>1</v>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Kolad tallhögstubbe</t>
+          <t>1 substratenheter # grova gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97362352</t>
+          <t>https://artportalen.se/Sighting/56357317</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>97362338</v>
+        <v>97362352</v>
       </c>
       <c r="B7" t="n">
-        <v>91909</v>
+        <v>81312</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,21 +1286,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1304,10 +1310,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569120</v>
+        <v>569144</v>
       </c>
       <c r="R7" t="n">
-        <v>7011613</v>
+        <v>7011434</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1351,6 +1357,11 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Kolad tallhögstubbe</t>
+        </is>
+      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
@@ -1369,54 +1380,54 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97362338</t>
+          <t>https://artportalen.se/Sighting/97362352</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>56357315</v>
+        <v>97362338</v>
       </c>
       <c r="B8" t="n">
-        <v>92083</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1503</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Pikhöjden, nordost om, Jmt</t>
+          <t>Nissemyran, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569157</v>
+        <v>569120</v>
       </c>
       <c r="R8" t="n">
-        <v>7011497</v>
+        <v>7011613</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1440,12 +1451,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2015-09-18</t>
+          <t>2021-06-17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2015-09-18</t>
+          <t>2021-06-17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1456,48 +1467,35 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>äldre tallskog på blockig morän</t>
-        </is>
-      </c>
-      <c r="AN8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>1 substratenheter # klen gammal tallåga</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Via Johan Staaf</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/56357315</t>
+          <t>https://artportalen.se/Sighting/97362338</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103997241</v>
+        <v>135641226</v>
       </c>
       <c r="B9" t="n">
-        <v>93197</v>
+        <v>92016</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1505,34 +1503,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Halbodarna, Jmt</t>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>569248</v>
+        <v>569136</v>
       </c>
       <c r="R9" t="n">
-        <v>7011329</v>
+        <v>7011417</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,22 +1557,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,74 +1574,80 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103997241</t>
+          <t>https://artportalen.se/Sighting/135641226</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103997281</v>
+        <v>135641224</v>
       </c>
       <c r="B10" t="n">
-        <v>92869</v>
+        <v>79950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4769</v>
+        <v>1353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Halbodarna, Jmt</t>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569069</v>
+        <v>569180</v>
       </c>
       <c r="R10" t="n">
-        <v>7011448</v>
+        <v>7011456</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1680,22 +1674,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1707,39 +1691,45 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103997281</t>
+          <t>https://artportalen.se/Sighting/135641224</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103997267</v>
+        <v>56357315</v>
       </c>
       <c r="B11" t="n">
-        <v>79327</v>
+        <v>92083</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1747,37 +1737,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Halbodarna, Jmt</t>
+          <t>Pikhöjden, nordost om, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>568989</v>
+        <v>569157</v>
       </c>
       <c r="R11" t="n">
-        <v>7011464</v>
+        <v>7011497</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1801,22 +1791,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:49</t>
+          <t>2015-09-18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:49</t>
+          <t>2015-09-18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1828,44 +1808,47 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>äldre tallskog på blockig morän</t>
+        </is>
+      </c>
+      <c r="AN11" t="n">
+        <v>1</v>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Tall</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
+          <t>1 substratenheter # klen gammal tallåga</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103997267</t>
+          <t>https://artportalen.se/Sighting/56357315</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>97362345</v>
+        <v>103997241</v>
       </c>
       <c r="B12" t="n">
-        <v>78730</v>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1873,34 +1856,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nissemyran, Jmt</t>
+          <t>Halbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569011</v>
+        <v>569248</v>
       </c>
       <c r="R12" t="n">
-        <v>7011496</v>
+        <v>7011329</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1927,12 +1910,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1944,9 +1937,9 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Kolad tallstubbe</t>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1962,21 +1955,21 @@
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97362345</t>
+          <t>https://artportalen.se/Sighting/103997241</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>97362347</v>
+        <v>135641213</v>
       </c>
       <c r="B13" t="n">
-        <v>83307</v>
+        <v>93313</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1984,34 +1977,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Nissemyran, Jmt</t>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569170</v>
+        <v>569153</v>
       </c>
       <c r="R13" t="n">
-        <v>7011440</v>
+        <v>7011355</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2038,12 +2031,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2058,31 +2051,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97362347</t>
+          <t>https://artportalen.se/Sighting/135641213</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>97362350</v>
+        <v>135641217</v>
       </c>
       <c r="B14" t="n">
-        <v>83307</v>
+        <v>93313</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2090,34 +2079,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nissemyran, Jmt</t>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569076</v>
+        <v>569217</v>
       </c>
       <c r="R14" t="n">
-        <v>7011466</v>
+        <v>7011326</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2144,12 +2133,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2160,40 +2149,31 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Äldre gran</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97362350</t>
+          <t>https://artportalen.se/Sighting/135641217</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>56357314</v>
+        <v>135641222</v>
       </c>
       <c r="B15" t="n">
-        <v>79084</v>
+        <v>93313</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2201,37 +2181,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Pikhöjden, nordost om, Jmt</t>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569164</v>
+        <v>569189</v>
       </c>
       <c r="R15" t="n">
-        <v>7011501</v>
+        <v>7011469</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2255,12 +2235,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2015-09-18</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2015-09-18</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2271,83 +2251,66 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>äldre tallskog på blockig morän</t>
-        </is>
-      </c>
-      <c r="AN15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>2 substratenheter # grov tallhögstubbe med spår av 4 bränder</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/56357314</t>
+          <t>https://artportalen.se/Sighting/135641222</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>97362348</v>
+        <v>103997281</v>
       </c>
       <c r="B16" t="n">
-        <v>79946</v>
+        <v>92869</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>4769</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nissemyran, Jmt</t>
+          <t>Halbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569215</v>
+        <v>569069</v>
       </c>
       <c r="R16" t="n">
-        <v>7011480</v>
+        <v>7011448</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2374,12 +2337,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2390,6 +2363,11 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2404,56 +2382,56 @@
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97362348</t>
+          <t>https://artportalen.se/Sighting/103997281</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>97362333</v>
+        <v>103997267</v>
       </c>
       <c r="B17" t="n">
-        <v>80432</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nissemyran, Jmt</t>
+          <t>Halbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569063</v>
+        <v>568989</v>
       </c>
       <c r="R17" t="n">
-        <v>7011469</v>
+        <v>7011464</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2480,12 +2458,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2496,6 +2484,16 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2510,56 +2508,56 @@
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97362333</t>
+          <t>https://artportalen.se/Sighting/103997267</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>97362341</v>
+        <v>135641216</v>
       </c>
       <c r="B18" t="n">
-        <v>80461</v>
+        <v>79411</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nissemyran, Jmt</t>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569064</v>
+        <v>569185</v>
       </c>
       <c r="R18" t="n">
-        <v>7011470</v>
+        <v>7011346</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2586,12 +2584,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2602,75 +2600,66 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97362341</t>
+          <t>https://artportalen.se/Sighting/135641216</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>97362335</v>
+        <v>135641218</v>
       </c>
       <c r="B19" t="n">
-        <v>79085</v>
+        <v>79411</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Nissemyran, Jmt</t>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>569218</v>
+        <v>569212</v>
       </c>
       <c r="R19" t="n">
-        <v>7011493</v>
+        <v>7011389</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2697,12 +2686,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2717,66 +2706,62 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97362335</t>
+          <t>https://artportalen.se/Sighting/135641218</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>97362344</v>
+        <v>135641223</v>
       </c>
       <c r="B20" t="n">
-        <v>79085</v>
+        <v>79411</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Nissemyran, Jmt</t>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569208</v>
+        <v>569151</v>
       </c>
       <c r="R20" t="n">
-        <v>7011579</v>
+        <v>7011451</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2803,12 +2788,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2819,35 +2804,46 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97362344</t>
+          <t>https://artportalen.se/Sighting/135641223</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>103997214</v>
+        <v>97362345</v>
       </c>
       <c r="B21" t="n">
-        <v>79085</v>
+        <v>78730</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2855,34 +2851,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Halbodarna, Jmt</t>
+          <t>Nissemyran, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569254</v>
+        <v>569011</v>
       </c>
       <c r="R21" t="n">
-        <v>7011325</v>
+        <v>7011496</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2909,22 +2905,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>13:31</t>
+          <t>2021-06-17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>13:31</t>
+          <t>2021-06-17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2936,9 +2922,9 @@
       <c r="AG21" t="b">
         <v>0</v>
       </c>
-      <c r="AS21" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Kolad tallstubbe</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2954,12 +2940,1681 @@
       </c>
       <c r="AY21" t="inlineStr">
         <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362345</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>97362347</v>
+      </c>
+      <c r="B22" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Nissemyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>569170</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7011440</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2021-06-17</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2021-06-17</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362347</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>97362350</v>
+      </c>
+      <c r="B23" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Nissemyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>569076</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7011466</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2021-06-17</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2021-06-17</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Äldre gran</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362350</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135641219</v>
+      </c>
+      <c r="B24" t="n">
+        <v>83398</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>569213</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7011405</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641219</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>56357314</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Pikhöjden, nordost om, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>569164</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7011501</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2015-09-18</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2015-09-18</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>äldre tallskog på blockig morän</t>
+        </is>
+      </c>
+      <c r="AN25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>2 substratenheter # grov tallhögstubbe med spår av 4 bränder</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56357314</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>97362348</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Nissemyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>569215</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7011480</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2021-06-17</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2021-06-17</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362348</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135641214</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80030</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>569203</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7011354</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641214</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>97362333</v>
+      </c>
+      <c r="B28" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Nissemyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>569063</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7011469</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2021-06-17</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2021-06-17</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362333</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>97362341</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Nissemyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>569064</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7011470</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2021-06-17</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2021-06-17</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362341</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135641221</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>569243</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7011412</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641221</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135641225</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99264</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>569173</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7011448</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641225</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>97362335</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Nissemyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>569218</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7011493</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2021-06-17</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2021-06-17</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362335</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>97362344</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Nissemyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>569208</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7011579</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2021-06-17</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2021-06-17</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362344</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>103997214</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Halbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>569254</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7011325</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
+      <c r="AZ34" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/103997214</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135641215</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79169</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>569203</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7011354</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641215</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135641211</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79434</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>569099</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7011352</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641211</t>
         </is>
       </c>
     </row>
@@ -2985,6 +4640,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43107-2023 artfynd.xlsx
+++ b/artfynd/A 43107-2023 artfynd.xlsx
@@ -1042,7 +1042,7 @@
         <v>135641212</v>
       </c>
       <c r="B5" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>135641226</v>
       </c>
       <c r="B9" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>135641224</v>
       </c>
       <c r="B10" t="n">
-        <v>79950</v>
+        <v>79977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>135641213</v>
       </c>
       <c r="B13" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>135641217</v>
       </c>
       <c r="B14" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>135641222</v>
       </c>
       <c r="B15" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>135641216</v>
       </c>
       <c r="B18" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>135641218</v>
       </c>
       <c r="B19" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>135641223</v>
       </c>
       <c r="B20" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>135641219</v>
       </c>
       <c r="B24" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3513,7 +3513,7 @@
         <v>135641214</v>
       </c>
       <c r="B27" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>135641225</v>
       </c>
       <c r="B31" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>135641215</v>
       </c>
       <c r="B35" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>135641211</v>
       </c>
       <c r="B36" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 43107-2023 artfynd.xlsx
+++ b/artfynd/A 43107-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ21"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1039,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>56357317</v>
+        <v>135641212</v>
       </c>
       <c r="B5" t="n">
-        <v>81312</v>
+        <v>79107</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1050,37 +1050,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1049</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Pikhöjden, nordost om, Jmt</t>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569134</v>
+        <v>569119</v>
       </c>
       <c r="R5" t="n">
-        <v>7011531</v>
+        <v>7011357</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2015-09-18</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2015-09-18</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,44 +1121,42 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>140-årig tallskog på blockig morän</t>
-        </is>
-      </c>
-      <c r="AN5" t="n">
-        <v>1</v>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>1 substratenheter # grova gammal tallhögstubbe</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/56357317</t>
+          <t>https://artportalen.se/Sighting/135641212</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97362352</v>
+        <v>56357317</v>
       </c>
       <c r="B6" t="n">
         <v>81312</v>
@@ -1189,17 +1187,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nissemyran, Jmt</t>
+          <t>Pikhöjden, nordost om, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569144</v>
+        <v>569134</v>
       </c>
       <c r="R6" t="n">
-        <v>7011434</v>
+        <v>7011531</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1223,12 +1221,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2015-09-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2015-09-18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,39 +1238,47 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>140-årig tallskog på blockig morän</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>1</v>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Kolad tallhögstubbe</t>
+          <t>1 substratenheter # grova gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97362352</t>
+          <t>https://artportalen.se/Sighting/56357317</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>97362338</v>
+        <v>97362352</v>
       </c>
       <c r="B7" t="n">
-        <v>91909</v>
+        <v>81312</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,21 +1286,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1304,10 +1310,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569120</v>
+        <v>569144</v>
       </c>
       <c r="R7" t="n">
-        <v>7011613</v>
+        <v>7011434</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1351,6 +1357,11 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Kolad tallhögstubbe</t>
+        </is>
+      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
@@ -1369,54 +1380,54 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97362338</t>
+          <t>https://artportalen.se/Sighting/97362352</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>56357315</v>
+        <v>97362338</v>
       </c>
       <c r="B8" t="n">
-        <v>92083</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1503</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Pikhöjden, nordost om, Jmt</t>
+          <t>Nissemyran, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569157</v>
+        <v>569120</v>
       </c>
       <c r="R8" t="n">
-        <v>7011497</v>
+        <v>7011613</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1440,12 +1451,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2015-09-18</t>
+          <t>2021-06-17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2015-09-18</t>
+          <t>2021-06-17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1456,48 +1467,35 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>äldre tallskog på blockig morän</t>
-        </is>
-      </c>
-      <c r="AN8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>1 substratenheter # klen gammal tallåga</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Via Johan Staaf</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/56357315</t>
+          <t>https://artportalen.se/Sighting/97362338</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103997241</v>
+        <v>135641226</v>
       </c>
       <c r="B9" t="n">
-        <v>93197</v>
+        <v>92048</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1505,34 +1503,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Halbodarna, Jmt</t>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>569248</v>
+        <v>569136</v>
       </c>
       <c r="R9" t="n">
-        <v>7011329</v>
+        <v>7011417</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,22 +1557,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,74 +1574,80 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103997241</t>
+          <t>https://artportalen.se/Sighting/135641226</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103997281</v>
+        <v>135641224</v>
       </c>
       <c r="B10" t="n">
-        <v>92869</v>
+        <v>79980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4769</v>
+        <v>1353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Halbodarna, Jmt</t>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569069</v>
+        <v>569180</v>
       </c>
       <c r="R10" t="n">
-        <v>7011448</v>
+        <v>7011456</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1680,22 +1674,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1707,39 +1691,45 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103997281</t>
+          <t>https://artportalen.se/Sighting/135641224</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103997267</v>
+        <v>56357315</v>
       </c>
       <c r="B11" t="n">
-        <v>79327</v>
+        <v>92083</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1747,37 +1737,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Halbodarna, Jmt</t>
+          <t>Pikhöjden, nordost om, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>568989</v>
+        <v>569157</v>
       </c>
       <c r="R11" t="n">
-        <v>7011464</v>
+        <v>7011497</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1801,22 +1791,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:49</t>
+          <t>2015-09-18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:49</t>
+          <t>2015-09-18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1828,44 +1808,47 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>äldre tallskog på blockig morän</t>
+        </is>
+      </c>
+      <c r="AN11" t="n">
+        <v>1</v>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Tall</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
+          <t>1 substratenheter # klen gammal tallåga</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103997267</t>
+          <t>https://artportalen.se/Sighting/56357315</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>97362345</v>
+        <v>103997241</v>
       </c>
       <c r="B12" t="n">
-        <v>78730</v>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1873,34 +1856,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nissemyran, Jmt</t>
+          <t>Halbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569011</v>
+        <v>569248</v>
       </c>
       <c r="R12" t="n">
-        <v>7011496</v>
+        <v>7011329</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1927,12 +1910,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1944,9 +1937,9 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Kolad tallstubbe</t>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1962,21 +1955,21 @@
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97362345</t>
+          <t>https://artportalen.se/Sighting/103997241</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>97362347</v>
+        <v>135641213</v>
       </c>
       <c r="B13" t="n">
-        <v>83307</v>
+        <v>93345</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1984,34 +1977,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Nissemyran, Jmt</t>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569170</v>
+        <v>569153</v>
       </c>
       <c r="R13" t="n">
-        <v>7011440</v>
+        <v>7011355</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2038,12 +2031,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2058,31 +2051,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97362347</t>
+          <t>https://artportalen.se/Sighting/135641213</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>97362350</v>
+        <v>135641217</v>
       </c>
       <c r="B14" t="n">
-        <v>83307</v>
+        <v>93345</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2090,34 +2079,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nissemyran, Jmt</t>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569076</v>
+        <v>569217</v>
       </c>
       <c r="R14" t="n">
-        <v>7011466</v>
+        <v>7011326</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2144,12 +2133,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2160,40 +2149,31 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Äldre gran</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97362350</t>
+          <t>https://artportalen.se/Sighting/135641217</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>56357314</v>
+        <v>135641222</v>
       </c>
       <c r="B15" t="n">
-        <v>79084</v>
+        <v>93345</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2201,37 +2181,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Pikhöjden, nordost om, Jmt</t>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569164</v>
+        <v>569189</v>
       </c>
       <c r="R15" t="n">
-        <v>7011501</v>
+        <v>7011469</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2255,12 +2235,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2015-09-18</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2015-09-18</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2271,83 +2251,66 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>äldre tallskog på blockig morän</t>
-        </is>
-      </c>
-      <c r="AN15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>2 substratenheter # grov tallhögstubbe med spår av 4 bränder</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/56357314</t>
+          <t>https://artportalen.se/Sighting/135641222</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>97362348</v>
+        <v>103997281</v>
       </c>
       <c r="B16" t="n">
-        <v>79946</v>
+        <v>92869</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>4769</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nissemyran, Jmt</t>
+          <t>Halbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569215</v>
+        <v>569069</v>
       </c>
       <c r="R16" t="n">
-        <v>7011480</v>
+        <v>7011448</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2374,12 +2337,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2390,6 +2363,11 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2404,56 +2382,56 @@
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97362348</t>
+          <t>https://artportalen.se/Sighting/103997281</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>97362333</v>
+        <v>103997267</v>
       </c>
       <c r="B17" t="n">
-        <v>80432</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nissemyran, Jmt</t>
+          <t>Halbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569063</v>
+        <v>568989</v>
       </c>
       <c r="R17" t="n">
-        <v>7011469</v>
+        <v>7011464</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2480,12 +2458,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2496,6 +2484,16 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2510,56 +2508,56 @@
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97362333</t>
+          <t>https://artportalen.se/Sighting/103997267</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>97362341</v>
+        <v>135641216</v>
       </c>
       <c r="B18" t="n">
-        <v>80461</v>
+        <v>79441</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nissemyran, Jmt</t>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569064</v>
+        <v>569185</v>
       </c>
       <c r="R18" t="n">
-        <v>7011470</v>
+        <v>7011346</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2586,12 +2584,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2602,75 +2600,66 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97362341</t>
+          <t>https://artportalen.se/Sighting/135641216</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>97362335</v>
+        <v>135641218</v>
       </c>
       <c r="B19" t="n">
-        <v>79085</v>
+        <v>79441</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Nissemyran, Jmt</t>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>569218</v>
+        <v>569212</v>
       </c>
       <c r="R19" t="n">
-        <v>7011493</v>
+        <v>7011389</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2697,12 +2686,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2717,66 +2706,62 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97362335</t>
+          <t>https://artportalen.se/Sighting/135641218</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>97362344</v>
+        <v>135641223</v>
       </c>
       <c r="B20" t="n">
-        <v>79085</v>
+        <v>79441</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Nissemyran, Jmt</t>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569208</v>
+        <v>569151</v>
       </c>
       <c r="R20" t="n">
-        <v>7011579</v>
+        <v>7011451</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2803,12 +2788,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2819,35 +2804,46 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97362344</t>
+          <t>https://artportalen.se/Sighting/135641223</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>103997214</v>
+        <v>97362345</v>
       </c>
       <c r="B21" t="n">
-        <v>79085</v>
+        <v>78730</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2855,34 +2851,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Halbodarna, Jmt</t>
+          <t>Nissemyran, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569254</v>
+        <v>569011</v>
       </c>
       <c r="R21" t="n">
-        <v>7011325</v>
+        <v>7011496</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2909,22 +2905,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>13:31</t>
+          <t>2021-06-17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>13:31</t>
+          <t>2021-06-17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2936,9 +2922,9 @@
       <c r="AG21" t="b">
         <v>0</v>
       </c>
-      <c r="AS21" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Kolad tallstubbe</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2954,12 +2940,1681 @@
       </c>
       <c r="AY21" t="inlineStr">
         <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362345</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>97362347</v>
+      </c>
+      <c r="B22" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Nissemyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>569170</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7011440</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2021-06-17</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2021-06-17</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362347</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>97362350</v>
+      </c>
+      <c r="B23" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Nissemyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>569076</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7011466</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2021-06-17</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2021-06-17</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Äldre gran</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362350</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135641219</v>
+      </c>
+      <c r="B24" t="n">
+        <v>83428</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>569213</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7011405</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641219</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>56357314</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Pikhöjden, nordost om, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>569164</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7011501</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2015-09-18</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2015-09-18</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>äldre tallskog på blockig morän</t>
+        </is>
+      </c>
+      <c r="AN25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>2 substratenheter # grov tallhögstubbe med spår av 4 bränder</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56357314</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>97362348</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Nissemyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>569215</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7011480</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2021-06-17</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2021-06-17</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362348</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135641214</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>569203</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7011354</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641214</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>97362333</v>
+      </c>
+      <c r="B28" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Nissemyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>569063</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7011469</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2021-06-17</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2021-06-17</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362333</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>97362341</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Nissemyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>569064</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7011470</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2021-06-17</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2021-06-17</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362341</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135641221</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>569243</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7011412</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641221</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135641225</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99296</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>569173</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7011448</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641225</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>97362335</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Nissemyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>569218</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7011493</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2021-06-17</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2021-06-17</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362335</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>97362344</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Nissemyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>569208</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7011579</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2021-06-17</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2021-06-17</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362344</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>103997214</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Halbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>569254</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7011325</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
+      <c r="AZ34" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/103997214</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135641215</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>569203</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7011354</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641215</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135641211</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>569099</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7011352</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641211</t>
         </is>
       </c>
     </row>
@@ -2985,6 +4640,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43107-2023 artfynd.xlsx
+++ b/artfynd/A 43107-2023 artfynd.xlsx
@@ -1495,7 +1495,7 @@
         <v>135641226</v>
       </c>
       <c r="B9" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>135641213</v>
       </c>
       <c r="B13" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>135641217</v>
       </c>
       <c r="B14" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>135641222</v>
       </c>
       <c r="B15" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>135641225</v>
       </c>
       <c r="B31" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 43107-2023 artfynd.xlsx
+++ b/artfynd/A 43107-2023 artfynd.xlsx
@@ -1042,7 +1042,7 @@
         <v>135641212</v>
       </c>
       <c r="B5" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>135641226</v>
       </c>
       <c r="B9" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>135641224</v>
       </c>
       <c r="B10" t="n">
-        <v>79980</v>
+        <v>79982</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>135641213</v>
       </c>
       <c r="B13" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>135641217</v>
       </c>
       <c r="B14" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>135641222</v>
       </c>
       <c r="B15" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>135641216</v>
       </c>
       <c r="B18" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>135641218</v>
       </c>
       <c r="B19" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>135641223</v>
       </c>
       <c r="B20" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>135641219</v>
       </c>
       <c r="B24" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3513,7 +3513,7 @@
         <v>135641214</v>
       </c>
       <c r="B27" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>135641221</v>
       </c>
       <c r="B30" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>135641225</v>
       </c>
       <c r="B31" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>135641215</v>
       </c>
       <c r="B35" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>135641211</v>
       </c>
       <c r="B36" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 43107-2023 artfynd.xlsx
+++ b/artfynd/A 43107-2023 artfynd.xlsx
@@ -1042,7 +1042,7 @@
         <v>135641212</v>
       </c>
       <c r="B5" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>135641226</v>
       </c>
       <c r="B9" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>135641224</v>
       </c>
       <c r="B10" t="n">
-        <v>79982</v>
+        <v>79983</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>135641213</v>
       </c>
       <c r="B13" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>135641217</v>
       </c>
       <c r="B14" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>135641222</v>
       </c>
       <c r="B15" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>135641216</v>
       </c>
       <c r="B18" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>135641218</v>
       </c>
       <c r="B19" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>135641223</v>
       </c>
       <c r="B20" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>135641219</v>
       </c>
       <c r="B24" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3513,7 +3513,7 @@
         <v>135641214</v>
       </c>
       <c r="B27" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>135641225</v>
       </c>
       <c r="B31" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>135641215</v>
       </c>
       <c r="B35" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>135641211</v>
       </c>
       <c r="B36" t="n">
-        <v>79466</v>
+        <v>79467</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 43107-2023 artfynd.xlsx
+++ b/artfynd/A 43107-2023 artfynd.xlsx
@@ -1495,7 +1495,7 @@
         <v>135641226</v>
       </c>
       <c r="B9" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>135641213</v>
       </c>
       <c r="B13" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>135641217</v>
       </c>
       <c r="B14" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>135641222</v>
       </c>
       <c r="B15" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>135641225</v>
       </c>
       <c r="B31" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 43107-2023 artfynd.xlsx
+++ b/artfynd/A 43107-2023 artfynd.xlsx
@@ -1042,7 +1042,7 @@
         <v>135641212</v>
       </c>
       <c r="B5" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>135641226</v>
       </c>
       <c r="B9" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>135641224</v>
       </c>
       <c r="B10" t="n">
-        <v>79983</v>
+        <v>79984</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>135641213</v>
       </c>
       <c r="B13" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>135641217</v>
       </c>
       <c r="B14" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>135641222</v>
       </c>
       <c r="B15" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>135641216</v>
       </c>
       <c r="B18" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>135641218</v>
       </c>
       <c r="B19" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>135641223</v>
       </c>
       <c r="B20" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>135641219</v>
       </c>
       <c r="B24" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3513,7 +3513,7 @@
         <v>135641214</v>
       </c>
       <c r="B27" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>135641221</v>
       </c>
       <c r="B30" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>135641225</v>
       </c>
       <c r="B31" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>135641215</v>
       </c>
       <c r="B35" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>135641211</v>
       </c>
       <c r="B36" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 43107-2023 artfynd.xlsx
+++ b/artfynd/A 43107-2023 artfynd.xlsx
@@ -1042,7 +1042,7 @@
         <v>135641212</v>
       </c>
       <c r="B5" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>135641226</v>
       </c>
       <c r="B9" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>135641224</v>
       </c>
       <c r="B10" t="n">
-        <v>79984</v>
+        <v>79988</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>135641213</v>
       </c>
       <c r="B13" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>135641217</v>
       </c>
       <c r="B14" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>135641222</v>
       </c>
       <c r="B15" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>135641216</v>
       </c>
       <c r="B18" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>135641218</v>
       </c>
       <c r="B19" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>135641223</v>
       </c>
       <c r="B20" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>135641219</v>
       </c>
       <c r="B24" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3513,7 +3513,7 @@
         <v>135641214</v>
       </c>
       <c r="B27" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>135641221</v>
       </c>
       <c r="B30" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>135641225</v>
       </c>
       <c r="B31" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>135641215</v>
       </c>
       <c r="B35" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>135641211</v>
       </c>
       <c r="B36" t="n">
-        <v>79468</v>
+        <v>79472</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
